--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:Q40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3105,6 +3105,686 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2.400%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2815740</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>58392</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>117643997</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>LBPM-134760659</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2.000%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>947532</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>19679</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>48022559</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>5.800%</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0.600%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>LBPM-134760659</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>05/12/2026</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-2505</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>38113</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>82636310</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13.400%</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-9.000%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>LBPM-134830628</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134830628/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>05/16/2026</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-2850</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5928</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1628231</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-25.000%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>LBPM-134866042</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134866042/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>20.600%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20.600%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>626568</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1825</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>3041592</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>22.500%</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>13.500%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ALSE-134545996</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>09/01/2025</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10.400%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>10.400%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>405242</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>785</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>3896556</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>23.700%</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0.300%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ALSE-134592232</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>06/22/2026</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1224399</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GMMX-134895766</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134895766/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>3030299</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GMMX-134491469</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q40"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1244,27 +1244,27 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1296,35 +1296,35 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>919714</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>82393</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65998147</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1381,35 +1381,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1083</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>211</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>187367</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1466,35 +1466,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>2.900%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>460749</t>
+          <t>919714</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>82064</v>
+        <v>82393</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>79723926</t>
+          <t>65998147</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>-3.500%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1551,35 +1551,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>791260</t>
+          <t>-1083</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58213</v>
+        <v>211</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>113037198</t>
+          <t>187367</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2.300%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134400261</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134400261/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/19/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1636,35 +1636,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460749</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>82064</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>103975400</t>
+          <t>79723926</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134490732</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>03/03/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1716,35 +1716,35 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>791260</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>8410</v>
+        <v>58213</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2375260</t>
+          <t>113037198</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>2.300%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134545039</t>
+          <t>ALSE-134400261</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134400261/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1786,80 +1786,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>05/19/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>223100</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1959</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3187140</t>
+          <t>103975400</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>117.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ALSE-134817781</t>
+          <t>ALSE-134490732</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134817781/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1871,55 +1871,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>205072</t>
+          <t>141982</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2371</v>
+        <v>8410</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2253383</t>
+          <t>2375260</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1929,7 +1929,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ALSE-134737223</t>
+          <t>ALSE-134545039</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1971,65 +1971,65 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>56.200%</t>
+          <t>13.800%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>130466</t>
+          <t>223100</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>833</v>
+        <v>1959</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>521588</t>
+          <t>3187140</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>117.200%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ALSE-134724096</t>
+          <t>ALSE-134817781</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134817781/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2056,65 +2056,65 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>14.600%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>284293</t>
+          <t>205072</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2758</v>
+        <v>2371</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4061334</t>
+          <t>2253383</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>2.700%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ALSE-134813879</t>
+          <t>ALSE-134737223</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2141,17 +2141,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>56.200%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-12.100%</t>
+          <t>25.000%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>130466</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>833</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>521588</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>40.200%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2161,7 +2184,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ALSE-134865728</t>
+          <t>ALSE-134724096</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2171,12 +2194,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2188,75 +2211,80 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>284293</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>158</v>
+        <v>2758</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>4061334</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ALSE-134447963</t>
+          <t>ALSE-134813879</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2296,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09/23/2025</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2278,40 +2306,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-3.900%</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-255942</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>6146</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>6562626</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>5.000%</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>-27.800%</t>
+          <t>-12.100%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2321,7 +2331,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>ALSE-134644319</t>
+          <t>ALSE-134865728</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2331,12 +2341,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2358,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2366,37 +2376,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.800%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1674655</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10432</v>
+        <v>158</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>20986911</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2406,7 +2411,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ALSE-134909157</t>
+          <t>ALSE-134447963</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2416,12 +2421,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134909157/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2433,80 +2438,75 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>09/23/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>12.500%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>396804</t>
+          <t>-255942</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3121</v>
+        <v>6146</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5668628</t>
+          <t>6562626</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>312.400%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-12.800%</t>
+          <t>-27.800%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ALSE-134810468</t>
+          <t>ALSE-134644319</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2518,80 +2518,80 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>-0.800%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4607862</t>
+          <t>-1674655</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>38731</v>
+        <v>10432</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>65826601</t>
+          <t>20986911</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>350.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-59.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALSE-134780087</t>
+          <t>ALSE-134909157</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134909157/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2603,80 +2603,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396804</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>3121</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3212622</t>
+          <t>5668628</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>312.400%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-12.800%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134810468</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2688,80 +2688,80 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4607862</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>38731</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1835614</t>
+          <t>65826601</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>350.000%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-59.000%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134780087</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4376605</t>
+          <t>3212622</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1835614</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2943,12 +2943,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4376605</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3028,27 +3028,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3058,25 +3058,25 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2904</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4824412</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>LBPM-134488487</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3133,35 +3133,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2815740</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>58392</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>117643997</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>LBPM-134488487</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3198,55 +3198,55 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>19679</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>48022559</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>5.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>LBPM-134399434</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3313,25 +3313,25 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-2505</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>38113</v>
+        <v>2904</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>82636310</t>
+          <t>4824412</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-9.000%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134830628</t>
+          <t>LBPM-134399434</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134830628/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3383,42 +3383,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>2.400%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2815740</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>58392</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>117643997</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>-0.200%</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-2850</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>5928</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>1628231</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-25.000%</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134866042</t>
+          <t>LBPM-134760659</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134866042/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3453,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3468,40 +3468,40 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>626568</t>
+          <t>947532</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1825</v>
+        <v>19679</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3041592</t>
+          <t>48022559</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>5.800%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>ALSE-134545996</t>
+          <t>LBPM-134760659</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3538,12 +3538,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>09/01/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3553,40 +3553,40 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>-12.700%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>405242</t>
+          <t>-3246916</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>785</v>
+        <v>48818</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>3896556</t>
+          <t>106745</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>ALSE-134592232</t>
+          <t>LBPM-134403897</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3623,12 +3623,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>05/12/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3653,50 +3653,50 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2505</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>38113</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1224399</t>
+          <t>82636310</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.000%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GMMX-134895766</t>
+          <t>LBPM-134830628</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134895766/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134830628/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3708,78 +3708,418 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>05/16/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>04.0004 Tenant Homeowners</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-2850</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>5928</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1628231</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-25.000%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>LBPM-134866042</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134866042/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>03/16/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>20.600%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20.600%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>626568</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1825</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>3041592</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>22.500%</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>13.500%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ALSE-134545996</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>09/01/2025</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10.400%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10.400%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>405242</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>785</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>3896556</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>23.700%</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0.300%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>ALSE-134592232</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>06/22/2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1224399</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GMMX-134895766</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134895766/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>06/23/2025</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Encompass Indemnity Company</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I40" t="n">
+      <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>3030299</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>GMMX-134491469</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>FILED</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>2025-04-11</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,55 +511,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.800%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>608726</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>20778</v>
+        <v>2878</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>27823328</t>
+          <t>4058170</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>41.700%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>ALSE-134353685</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134353685/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -596,55 +596,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>223598</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>290956</v>
+        <v>3250</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>238742051</t>
+          <t>5884151</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24.500%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>ALSE-134355084</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134355084/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -681,55 +681,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-554469</t>
+          <t>7487529</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>20679</v>
+        <v>36065</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>26357498</t>
+          <t>49916861</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>388.400%</t>
+          <t>39.100%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-41.500%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>ALSE-134355105</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134355105/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -766,55 +766,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.700%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-25716996</t>
+          <t>210679</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>360274</v>
+        <v>2038</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>263832752</t>
+          <t>3453760</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>847.900%</t>
+          <t>6.300%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-52.200%</t>
+          <t>4.000%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>ALSE-134358345</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134358345/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -851,80 +851,80 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07/15/2026</t>
+          <t>03/03/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>72.800%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>12805106</t>
+          <t>791260</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>93081</v>
+        <v>58213</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>129346241</t>
+          <t>113037198</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>74.100%</t>
+          <t>2.300%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SFMA-134872376</t>
+          <t>ALSE-134400261</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134872376/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134400261/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -954,37 +954,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-11.900%</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-7.500%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-130787</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1447</v>
+        <v>158</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1741509</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-11.500%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GECC-134894381</t>
+          <t>ALSE-134447963</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1004,12 +999,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1016,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>05/19/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1041,35 +1036,35 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-12.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-7.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-617584</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>9434</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8256468</t>
+          <t>103975400</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-11.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1079,7 +1074,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GECC-134894381</t>
+          <t>ALSE-134490732</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1089,12 +1084,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1101,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1121,35 +1116,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141982</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>8410</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2375260</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1159,27 +1154,27 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>GECC-134601148</t>
+          <t>ALSE-134545039</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1186,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>09/23/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1209,62 +1204,57 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-255942</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>6146</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6562626</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-27.800%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GECC-134601148</t>
+          <t>ALSE-134644319</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1266,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1314,7 +1304,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3212622</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1334,7 +1324,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1334,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1351,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1399,7 +1389,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1835614</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1419,7 +1409,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1419,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1436,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1466,35 +1456,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>919714</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>82393</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>65998147</t>
+          <t>4376605</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1504,7 +1494,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1514,12 +1504,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1531,55 +1521,55 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>56.200%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1083</t>
+          <t>130466</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>211</v>
+        <v>833</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>187367</t>
+          <t>521588</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>40.200%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,7 +1579,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>ALSE-134724096</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1599,12 +1589,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1616,55 +1606,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>460749</t>
+          <t>205072</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>82064</v>
+        <v>2371</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79723926</t>
+          <t>2253383</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>2.700%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1674,7 +1664,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>ALSE-134737223</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1684,12 +1674,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1701,80 +1691,80 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>791260</t>
+          <t>4607862</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>58213</v>
+        <v>38731</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>113037198</t>
+          <t>65826601</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2.300%</t>
+          <t>350.000%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-59.000%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134400261</t>
+          <t>ALSE-134780087</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134400261/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1786,80 +1776,80 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>05/19/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>396804</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3121</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>103975400</t>
+          <t>5668628</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>312.400%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-12.800%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ALSE-134490732</t>
+          <t>ALSE-134810468</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1871,80 +1861,80 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>284293</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>8410</v>
+        <v>2758</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2375260</t>
+          <t>4061334</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ALSE-134545039</t>
+          <t>ALSE-134813879</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2031,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2056,40 +2046,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9.100%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>205072</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>2371</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2253383</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>10.700%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>2.700%</t>
+          <t>-12.100%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2099,7 +2066,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ALSE-134737223</t>
+          <t>ALSE-134865728</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2109,12 +2076,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2093,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>03/16/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2141,40 +2108,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>56.200%</t>
+          <t>20.600%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>20.600%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>130466</t>
+          <t>626568</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>833</v>
+        <v>1825</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>521588</t>
+          <t>3041592</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2184,7 +2151,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ALSE-134724096</t>
+          <t>ALSE-134545996</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2194,12 +2161,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2211,80 +2178,80 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>09/01/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>14.600%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>284293</t>
+          <t>405242</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2758</v>
+        <v>785</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4061334</t>
+          <t>3896556</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>23.700%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>0.300%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ALSE-134813879</t>
+          <t>ALSE-134592232</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2296,22 +2263,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2321,7 +2288,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-12.100%</t>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3030299</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2331,7 +2321,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>ALSE-134865728</t>
+          <t>GMMX-134491469</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2341,12 +2331,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2358,12 +2348,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2376,57 +2366,62 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ALSE-134447963</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2433,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>09/23/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2456,57 +2451,62 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-255942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>6146</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6562626</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-27.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ALSE-134644319</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2518,12 +2518,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2543,20 +2543,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1674655</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>10432</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20986911</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALSE-134909157</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134909157/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2603,80 +2603,80 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>396804</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3121</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5668628</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>312.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-12.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALSE-134810468</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2688,80 +2688,80 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>-11.900%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>-7.500%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4607862</t>
+          <t>-130787</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>38731</v>
+        <v>1447</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>65826601</t>
+          <t>1741509</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>350.000%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-59.000%</t>
+          <t>-11.500%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ALSE-134780087</t>
+          <t>GECC-134894381</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2773,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2793,35 +2793,35 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-12.400%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.500%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-617584</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>9434</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>3212622</t>
+          <t>8256468</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.100%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.700%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>GECC-134894381</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2858,55 +2858,55 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-137094</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1835614</t>
+          <t>1960106</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.300%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.000%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>LBPM-134347248</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347248/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2943,55 +2943,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4203</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4376605</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.800%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>LBPM-134347722</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3048,35 +3048,35 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-104843</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1003</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1492141</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.400%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.600%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>LBPM-134347722</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3096,12 +3096,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3113,55 +3113,55 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/21/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1118</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21563</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.400%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>LBPM-134347807</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>01/21/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3218,35 +3218,35 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-56053</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>301</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1112402</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-12.400%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>LBPM-134347807</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3283,12 +3283,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>01/21/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3303,35 +3303,35 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>-1386</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2904</v>
+        <v>9</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4824412</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>-9.400%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>LBPM-134347807</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3368,55 +3368,55 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2815740</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>58392</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>117643997</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>LBPM-134399434</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3453,55 +3453,55 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>19679</v>
+        <v>2904</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>48022559</t>
+          <t>4824412</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>5.800%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>LBPM-134399434</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3538,55 +3538,55 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-12.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-3246916</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>48818</v>
+        <v>0</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>106745</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>LBPM-134403897</t>
+          <t>LBPM-134488487</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3623,27 +3623,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05/12/2026</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3653,25 +3653,25 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-2505</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>38113</v>
+        <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>82636310</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-9.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LBPM-134830628</t>
+          <t>LBPM-134488487</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3691,12 +3691,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134830628/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3708,55 +3708,55 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>05/16/2026</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>2.900%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-2850</t>
+          <t>919714</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5928</v>
+        <v>82393</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1628231</t>
+          <t>65998147</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-25.000%</t>
+          <t>-3.500%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>LBPM-134866042</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134866042/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3793,55 +3793,55 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>626568</t>
+          <t>-1083</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1825</v>
+        <v>211</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3041592</t>
+          <t>187367</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>ALSE-134545996</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3861,12 +3861,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3878,12 +3878,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>09/01/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3898,35 +3898,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>405242</t>
+          <t>460749</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>785</v>
+        <v>82064</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>3896556</t>
+          <t>79723926</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>ALSE-134592232</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3963,12 +3963,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>06/22/2026</t>
+          <t>03/16/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3978,35 +3978,35 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.400%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>465032</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>14290</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1224399</t>
+          <t>5306519</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>19.900%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4016,27 +4016,27 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>rate_change_pending</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GMMX-134895766</t>
+          <t>LBPM-134326132</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134895766/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134326132/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4048,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4063,65 +4063,915 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-12.700%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-3246916</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>48818</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>106745</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-7.300%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>LBPM-134403897</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2.400%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2815740</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>58392</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>117643997</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>LBPM-134760659</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2.000%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>947532</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>19679</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>48022559</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5.800%</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0.600%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>LBPM-134760659</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>3030299</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
+      <c r="I47" t="n">
+        <v>20778</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>27823328</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>41.700%</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-26.900%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>GMMX-134491469</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>SFMA-134294867</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
         <is>
           <t>FILED</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>290956</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>238742051</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>24.500%</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-26.900%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SFMA-134294867</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>02/03/2025</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>22213</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>28615291</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>19.400%</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>-13.500%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SFMA-134329519</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>02/03/2025</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-5758545</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>356711</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>261203324</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>-17.100%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>SFMA-134329519</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>15.900%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-2.100%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-554469</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>20679</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>26357498</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>388.400%</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-41.500%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SFMA-134676753</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-9.700%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-25716996</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>360274</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>263832752</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>847.900%</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>-52.200%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SFMA-134676753</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>01/25/2025</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>19.100%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>8.300%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>737882</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>5911</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>8890145</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>17.700%</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>TRVD-G134249162</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>01/25/2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>19.100%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>34845</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>280</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>395965</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>17.200%</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>TRVD-G134249162</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,7 +936,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>09/23/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>-255942</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>158</v>
+        <v>6146</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>6562626</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>-27.800%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134447963</t>
+          <t>ALSE-134644319</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -999,12 +999,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>05/19/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>103975400</t>
+          <t>3212622</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134490732</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1116,35 +1116,35 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>8410</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2375260</t>
+          <t>1835614</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134545039</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09/23/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1204,32 +1204,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-255942</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>6146</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6562626</t>
+          <t>4376605</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-27.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1239,7 +1244,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134644319</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1249,12 +1254,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1271,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1276,45 +1281,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>56.200%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>130466</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>833</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3212622</t>
+          <t>521588</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>40.200%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1324,7 +1329,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134724096</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1334,12 +1339,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1351,55 +1356,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205072</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>2371</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1835614</t>
+          <t>2253383</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.700%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1409,7 +1414,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134737223</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1419,12 +1424,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1436,80 +1441,80 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4607862</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>38731</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4376605</t>
+          <t>65826601</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>350.000%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-59.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134780087</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1526,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1536,65 +1541,65 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>56.200%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>130466</t>
+          <t>396804</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>833</v>
+        <v>3121</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>521588</t>
+          <t>5668628</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>312.400%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>-12.800%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134724096</t>
+          <t>ALSE-134810468</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1611,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1621,65 +1626,65 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>205072</t>
+          <t>284293</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2371</v>
+        <v>2758</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2253383</t>
+          <t>4061334</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2.700%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134737223</t>
+          <t>ALSE-134813879</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1701,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1711,7 +1716,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>13.800%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1721,25 +1726,25 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4607862</t>
+          <t>223100</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>38731</v>
+        <v>1959</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>65826601</t>
+          <t>3187140</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>350.000%</t>
+          <t>117.200%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-59.000%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1749,7 +1754,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134780087</t>
+          <t>ALSE-134817781</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1759,12 +1764,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134817781/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1781,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1796,60 +1801,37 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.000%</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>396804</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>3121</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>5668628</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>312.400%</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>-12.800%</t>
+          <t>-12.100%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ALSE-134810468</t>
+          <t>ALSE-134865728</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1861,12 +1843,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>03/16/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1881,60 +1863,60 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.600%</t>
+          <t>20.600%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>20.600%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>284293</t>
+          <t>626568</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2758</v>
+        <v>1825</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4061334</t>
+          <t>3041592</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ALSE-134813879</t>
+          <t>ALSE-134545996</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1946,80 +1928,80 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>09/01/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13.800%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>223100</t>
+          <t>405242</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1959</v>
+        <v>785</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3187140</t>
+          <t>3896556</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>117.200%</t>
+          <t>23.700%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>0.300%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ALSE-134817781</t>
+          <t>ALSE-134592232</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134817781/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2031,22 +2013,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2056,7 +2038,30 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-12.100%</t>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>3030299</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2066,7 +2071,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ALSE-134865728</t>
+          <t>GMMX-134491469</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2076,12 +2081,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2093,80 +2098,80 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>626568</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1825</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3041592</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ALSE-134545996</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2183,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09/01/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2198,60 +2203,60 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>405242</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>785</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3896556</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ALSE-134592232</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2268,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2301,7 +2306,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>3030299</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2321,7 +2326,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GMMX-134491469</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2331,12 +2336,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2358,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2401,27 +2406,27 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GECC-134601148</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2433,7 +2438,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2453,60 +2458,60 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.900%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.500%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-130787</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1447</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1741509</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.500%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GECC-134601148</t>
+          <t>GECC-134894381</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2523,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2538,35 +2543,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-12.400%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.500%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-617584</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>9434</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8256468</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.100%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.700%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2576,7 +2581,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>GECC-134894381</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2586,12 +2591,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2603,55 +2608,55 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>02/05/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-137094</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1960106</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-6.300%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.000%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2661,7 +2666,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>LBPM-134347248</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2671,12 +2676,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347248/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2688,55 +2693,55 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-11.900%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.500%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-130787</t>
+          <t>-4203</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1447</v>
+        <v>29</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1741509</t>
+          <t>59666</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>-5.800%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-11.500%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2746,7 +2751,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>GECC-134894381</t>
+          <t>LBPM-134347722</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2756,12 +2761,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2773,55 +2778,55 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>01/01/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-12.400%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.500%</t>
+          <t>-7.000%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-617584</t>
+          <t>-104843</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9434</v>
+        <v>1003</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8256468</t>
+          <t>1492141</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-1.100%</t>
+          <t>-5.400%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-11.700%</t>
+          <t>-7.600%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2831,7 +2836,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>GECC-134894381</t>
+          <t>LBPM-134347722</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2841,12 +2846,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2858,57 +2863,57 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>01/21/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-1118</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>4</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>21563</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>-7.000%</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>-137094</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>478</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>1960106</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>-6.300%</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>-11.000%</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -2916,7 +2921,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>LBPM-134347248</t>
+          <t>LBPM-134347807</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2926,12 +2931,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347248/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2943,55 +2948,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/21/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-4203</t>
+          <t>-56053</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>301</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>1112402</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-5.800%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-12.400%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3001,7 +3006,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>LBPM-134347722</t>
+          <t>LBPM-134347807</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3011,12 +3016,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3028,55 +3033,55 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/21/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>The First Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-104843</t>
+          <t>-1386</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1003</v>
+        <v>9</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1492141</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-5.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-7.600%</t>
+          <t>-9.400%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3086,7 +3091,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>LBPM-134347722</t>
+          <t>LBPM-134347807</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3096,12 +3101,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2024-12-13</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3113,12 +3118,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/21/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3133,35 +3138,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-1118</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3171,7 +3176,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LBPM-134347807</t>
+          <t>LBPM-134399434</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3181,12 +3186,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3198,12 +3203,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01/21/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3218,35 +3223,35 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>1.300%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-56053</t>
+          <t>208</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>301</v>
+        <v>2904</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1112402</t>
+          <t>4824412</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-12.400%</t>
+          <t>-10.000%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3256,7 +3261,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134347807</t>
+          <t>LBPM-134399434</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3266,12 +3271,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3283,45 +3288,45 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01/21/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-1386</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3331,7 +3336,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-9.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3341,7 +3346,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134347807</t>
+          <t>LBPM-134488487</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3351,12 +3356,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3368,22 +3373,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3426,7 +3431,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>LBPM-134488487</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3436,12 +3441,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3453,12 +3458,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3468,40 +3473,40 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>2.900%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>919714</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2904</v>
+        <v>82393</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4824412</t>
+          <t>65998147</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>-3.500%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3511,7 +3516,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3521,12 +3526,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3538,55 +3543,55 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Progressive Northern Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1083</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187367</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3596,7 +3601,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3606,12 +3611,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3623,55 +3628,55 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Progressive Northwestern Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.600%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>460749</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>82064</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79723926</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3681,7 +3686,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>PRGS-134368750</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3691,12 +3696,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-01-10</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3713,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>03/16/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3723,40 +3728,40 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>9.400%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>919714</t>
+          <t>465032</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>82393</v>
+        <v>14290</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>65998147</t>
+          <t>5306519</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>19.900%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-3.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3766,7 +3771,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>LBPM-134326132</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3776,12 +3781,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134326132/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3793,12 +3798,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3808,40 +3813,40 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>-12.700%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-1083</t>
+          <t>-3246916</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>211</v>
+        <v>48818</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>187367</t>
+          <t>106745</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3851,7 +3856,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>LBPM-134403897</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3861,12 +3866,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3878,55 +3883,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>460749</t>
+          <t>2815740</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>82064</v>
+        <v>58392</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>79723926</t>
+          <t>117643997</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3936,7 +3941,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>LBPM-134760659</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3946,12 +3951,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3968,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>03/16/2025</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3973,45 +3978,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9.400%</t>
+          <t>4.500%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>465032</t>
+          <t>947532</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>14290</v>
+        <v>19679</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5306519</t>
+          <t>48022559</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>19.900%</t>
+          <t>5.800%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4021,7 +4026,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LBPM-134326132</t>
+          <t>LBPM-134760659</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4031,12 +4036,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134326132/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4048,12 +4053,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4063,40 +4068,40 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-12.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-3246916</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>48818</v>
+        <v>20778</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>106745</t>
+          <t>27823328</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>41.700%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-26.900%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4106,7 +4111,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>LBPM-134403897</t>
+          <t>SFMA-134294867</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4116,12 +4121,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4133,55 +4138,55 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2815740</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>58392</v>
+        <v>290956</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>117643997</t>
+          <t>238742051</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>24.500%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>-26.900%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4191,7 +4196,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>SFMA-134294867</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4201,12 +4206,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4218,55 +4223,55 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>19679</v>
+        <v>22213</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>48022559</t>
+          <t>28615291</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>5.800%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>-13.500%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4276,7 +4281,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>SFMA-134329519</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4286,12 +4291,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4303,12 +4308,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4318,40 +4323,40 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.200%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5758545</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>20778</v>
+        <v>356711</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>27823328</t>
+          <t>261203324</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>41.700%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>-17.100%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4361,7 +4366,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>SFMA-134329519</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4371,12 +4376,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4388,12 +4393,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4403,40 +4408,40 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.100%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-554469</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>290956</v>
+        <v>20679</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>238742051</t>
+          <t>26357498</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>24.500%</t>
+          <t>388.400%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>-41.500%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4446,7 +4451,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>SFMA-134676753</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4456,12 +4461,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4473,12 +4478,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4493,35 +4498,35 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.700%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>-25716996</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>22213</v>
+        <v>360274</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>28615291</t>
+          <t>263832752</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>847.900%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-13.500%</t>
+          <t>-52.200%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4531,7 +4536,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SFMA-134329519</t>
+          <t>SFMA-134676753</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4541,12 +4546,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4558,55 +4563,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>01/25/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>8.300%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-5758545</t>
+          <t>737882</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>356711</v>
+        <v>5911</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>261203324</t>
+          <t>8890145</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>17.700%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-17.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4616,7 +4621,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>SFMA-134329519</t>
+          <t>TRVD-G134249162</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4626,12 +4631,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4643,55 +4648,55 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/25/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-554469</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>20679</v>
+        <v>280</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>26357498</t>
+          <t>395965</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>388.400%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-41.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4701,7 +4706,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>TRVD-G134249162</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4711,12 +4716,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4733,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4743,40 +4748,40 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-9.700%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-25716996</t>
+          <t>-51280</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>360274</v>
+        <v>2534</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>263832752</t>
+          <t>2226049</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>847.900%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-52.200%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4786,7 +4791,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>GNSC-134806133</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4796,12 +4801,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4813,55 +4818,50 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/25/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>19.100%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>8.300%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>737882</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>5911</v>
+        <v>158</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>8890145</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>17.700%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>TRVD-G134249162</t>
+          <t>ALSE-134447963</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4898,50 +4898,50 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/25/2025</t>
+          <t>05/19/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>103975400</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>TRVD-G134249162</t>
+          <t>ALSE-134490732</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4966,12 +4966,97 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>6.000%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>141982</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>8410</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2375260</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7.400%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ALSE-134545039</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2025-05-23</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3908,30 +3908,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2815740</t>
+          <t>947532</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>58392</v>
+        <v>19679</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>117643997</t>
+          <t>48022559</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>5.800%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>0.600%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3968,55 +3968,55 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>19679</v>
+        <v>20778</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>48022559</t>
+          <t>27823328</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>5.800%</t>
+          <t>41.700%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>-26.900%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>SFMA-134294867</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4087,16 +4087,16 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>20778</v>
+        <v>290956</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>27823328</t>
+          <t>238742051</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>41.700%</t>
+          <t>24.500%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.300%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4168,25 +4168,25 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>290956</v>
+        <v>22213</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>238742051</t>
+          <t>28615291</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24.500%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>-13.500%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>SFMA-134329519</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4243,35 +4243,35 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-5758545</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>356711</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>261203324</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>13.300%</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>22213</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>28615291</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>19.400%</t>
-        </is>
-      </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-13.500%</t>
+          <t>-17.100%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>01/02/2026</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4328,35 +4328,35 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>-2.100%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-5758545</t>
+          <t>-554469</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>356711</v>
+        <v>20679</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>261203324</t>
+          <t>26357498</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>388.400%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-17.100%</t>
+          <t>-41.500%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134329519</t>
+          <t>SFMA-134676753</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4376,12 +4376,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4413,35 +4413,35 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>-9.700%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-554469</t>
+          <t>-25716996</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>20679</v>
+        <v>360274</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>26357498</t>
+          <t>263832752</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>388.400%</t>
+          <t>847.900%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-41.500%</t>
+          <t>-52.200%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4478,55 +4478,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>01/25/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-9.700%</t>
+          <t>8.300%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-25716996</t>
+          <t>737882</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>360274</v>
+        <v>5911</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>263832752</t>
+          <t>8890145</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>847.900%</t>
+          <t>17.700%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-52.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>TRVD-G134249162</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4588,25 +4588,25 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8.300%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>737882</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5911</v>
+        <v>280</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>8890145</t>
+          <t>395965</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17.700%</t>
+          <t>17.200%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4648,55 +4648,55 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/25/2025</t>
+          <t>01/23/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>-0.100%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>-51280</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>280</v>
+        <v>2534</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>2226049</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>TRVD-G134249162</t>
+          <t>GNSC-134806133</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4716,12 +4716,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4733,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01/23/2026</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MGA Insurance Company, Inc.</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4751,37 +4751,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>3.700%</t>
-        </is>
-      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-51280</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>2534</v>
+        <v>158</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2226049</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4791,7 +4786,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GNSC-134806133</t>
+          <t>ALSE-134447963</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4801,12 +4796,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4813,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>05/19/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4836,32 +4831,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>103975400</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ALSE-134447963</t>
+          <t>ALSE-134490732</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4881,12 +4881,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>05/19/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4913,35 +4913,35 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141982</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>8410</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>103975400</t>
+          <t>2375260</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ALSE-134490732</t>
+          <t>ALSE-134545039</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4966,95 +4966,10 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
-        <is>
-          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>06/23/2025</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>19.0 Personal Auto</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>19.0004 Other</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>6.000%</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>6.000%</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>141982</t>
-        </is>
-      </c>
-      <c r="I55" t="n">
-        <v>8410</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2375260</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>7.400%</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>ALSE-134545039</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>FILED</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>2025-05-23</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
         <is>
           <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q54"/>
+  <dimension ref="A1:R113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>source_pdf</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>validation_tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,12 +516,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>01/22/2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -531,7 +536,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15.800%</t>
+          <t>24.300%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -541,25 +546,25 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>608726</t>
+          <t>6157866</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2878</v>
+        <v>33018</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4058170</t>
+          <t>41052441</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18.600%</t>
+          <t>36.900%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +574,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ALSE-134353685</t>
+          <t>ALSE-133920243</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +584,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2024-12-16</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134353685/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133920243/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -596,12 +606,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>01/22/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -616,35 +626,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>21.200%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>223598</t>
+          <t>582175</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3250</v>
+        <v>3174</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5884151</t>
+          <t>3881165</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>19.500%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2.600%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,7 +664,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-134355084</t>
+          <t>ALSE-133922065</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -664,12 +674,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2023-12-13</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134355084/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133922065/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -681,12 +696,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>01/22/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -701,7 +716,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -711,25 +726,25 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>7487529</t>
+          <t>503530</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>36065</v>
+        <v>2259</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>49916861</t>
+          <t>3356864</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>39.100%</t>
+          <t>18.700%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +754,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-134355105</t>
+          <t>ALSE-133923427</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +764,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134355105/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133923427/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -766,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01/20/2025</t>
+          <t>01/22/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -786,35 +806,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6.100%</t>
+          <t>17.400%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.100%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>210679</t>
+          <t>849881</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2038</v>
+        <v>3651</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3453760</t>
+          <t>5665875</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6.300%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4.000%</t>
+          <t>9.400%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -824,7 +844,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-134358345</t>
+          <t>ALSE-133924608</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -834,12 +854,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2023-12-15</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134358345/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133924608/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -851,7 +876,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03/03/2025</t>
+          <t>07/15/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -871,30 +896,30 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>791260</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>58213</v>
+        <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>113037198</t>
+          <t>89372468</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -909,7 +934,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-134400261</t>
+          <t>ALSE-134145361</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -919,12 +944,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134400261/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134145361/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -936,12 +966,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09/23/2025</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -954,32 +984,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>24.500%</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.900%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-255942</t>
+          <t>628001</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>6146</v>
+        <v>2835</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6562626</t>
+          <t>4186673</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>5.000%</t>
+          <t>38.900%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-27.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -989,7 +1024,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134644319</t>
+          <t>ALSE-134163422</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -999,12 +1034,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2024-06-28</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134163422/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1056,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>08/05/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1036,30 +1076,30 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061561</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>55632</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3212622</t>
+          <t>108503188</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.200%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1074,7 +1114,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134168088</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1084,12 +1124,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134168088/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1146,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1139,7 +1184,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1835614</t>
+          <t>3399134</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1159,7 +1204,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134230449</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1169,12 +1214,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134230449/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1236,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1224,7 +1274,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4376605</t>
+          <t>1913742</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1244,7 +1294,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134645740</t>
+          <t>ALSE-134230449</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1254,12 +1304,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134230449/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1271,55 +1326,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>10/07/2024</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>56.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>25.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>130466</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>833</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>521588</t>
+          <t>4249882</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1329,7 +1384,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134724096</t>
+          <t>ALSE-134230449</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1339,12 +1394,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134230449/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1416,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01/12/2026</t>
+          <t>11/25/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1376,35 +1436,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>6.400%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>6.400%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>205072</t>
+          <t>111365</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2371</v>
+        <v>2043</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2253383</t>
+          <t>1742286</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>10.700%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2.700%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1414,7 +1474,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134737223</t>
+          <t>ALSE-134296907</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1424,12 +1484,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134296907/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1506,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>11/25/2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1456,65 +1521,70 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>49.000%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>15.000%</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>7.000%</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4607862</t>
+          <t>69253</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>38731</v>
+        <v>859</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>65826601</t>
+          <t>462312</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>350.000%</t>
+          <t>31.200%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-59.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134780087</t>
+          <t>ALSE-134297132</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2024-10-25</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134297132/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1526,80 +1596,80 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>12/09/2024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>12.500%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>-9.100%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>396804</t>
+          <t>-13487</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3121</v>
+        <v>156</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5668628</t>
+          <t>148204</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>312.400%</t>
+          <t>-5.200%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-12.800%</t>
+          <t>-10.600%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134810468</t>
+          <t>ALSE-134311611</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134311611/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1681,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1631,60 +1701,65 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>14.600%</t>
+          <t>15.800%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>284293</t>
+          <t>608726</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2758</v>
+        <v>2878</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4061334</t>
+          <t>4058170</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>10.900%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3.600%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134813879</t>
+          <t>ALSE-134353685</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2024-12-16</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134353685/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1771,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>03/02/2026</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1716,60 +1791,65 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13.800%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>223100</t>
+          <t>223598</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1959</v>
+        <v>3250</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3187140</t>
+          <t>5884151</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>117.200%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134817781</t>
+          <t>ALSE-134355084</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134817781/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134355084/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1861,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04/14/2026</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1801,12 +1881,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-12.100%</t>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>7487529</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>36065</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>49916861</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>39.100%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1816,7 +1919,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ALSE-134865728</t>
+          <t>ALSE-134355105</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1826,12 +1929,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134355105/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1843,12 +1951,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>03/16/2026</t>
+          <t>01/20/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1863,35 +1971,35 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20.600%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>626568</t>
+          <t>210679</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1825</v>
+        <v>2038</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>3041592</t>
+          <t>3453760</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>6.300%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>4.000%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1901,7 +2009,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ALSE-134545996</t>
+          <t>ALSE-134358345</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1911,12 +2019,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134358345/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1928,12 +2041,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09/01/2025</t>
+          <t>03/03/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1948,35 +2061,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>0.700%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>405242</t>
+          <t>791260</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>785</v>
+        <v>58213</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>3896556</t>
+          <t>113037198</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>2.300%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1986,7 +2099,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ALSE-134592232</t>
+          <t>ALSE-134400261</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1996,12 +2109,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134400261/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2131,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>07/08/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2031,37 +2149,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.000%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>3030299</t>
+          <t>138001</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2071,7 +2184,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GMMX-134491469</t>
+          <t>ALSE-134447963</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2081,12 +2194,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2216,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>05/19/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2136,7 +2254,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>103975400</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2151,27 +2269,32 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GECC-134601148</t>
+          <t>ALSE-134490732</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2306,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2198,35 +2321,35 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.000%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>141982</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>8410</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2375260</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2236,27 +2359,32 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>rate_change_withdrawn</t>
+          <t>rate_change</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GECC-134601148</t>
+          <t>ALSE-134545039</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>WITHDRAWN</t>
+          <t>FILED</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2396,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>09/23/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2286,37 +2414,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.900%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-255942</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>6146</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6562626</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.000%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-27.800%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2326,7 +2449,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>ALSE-134644319</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2336,12 +2459,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134644319/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2481,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>05/08/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2391,7 +2519,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3212622</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2411,7 +2539,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GECC-134653021</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2421,12 +2549,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2571,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GEICO Marine Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2458,35 +2591,35 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-11.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-7.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-130787</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1447</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1741509</t>
+          <t>1835614</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-11.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2496,7 +2629,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GECC-134894381</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2506,12 +2639,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2661,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/03/2026</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2543,35 +2681,35 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-12.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-7.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-617584</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>9434</v>
+        <v>0</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8256468</t>
+          <t>4376605</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-11.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2581,7 +2719,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GECC-134894381</t>
+          <t>ALSE-134645740</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2591,12 +2729,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134645740/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2751,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>02/05/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2623,40 +2766,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>56.200%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>25.000%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-137094</t>
+          <t>130466</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>478</v>
+        <v>833</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1960106</t>
+          <t>521588</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-6.300%</t>
+          <t>40.200%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-11.000%</t>
+          <t>4.300%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2666,7 +2809,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>LBPM-134347248</t>
+          <t>ALSE-134724096</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2676,12 +2819,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347248/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134724096/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2693,12 +2841,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>01/12/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2708,40 +2856,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-4203</t>
+          <t>205072</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>2371</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>59666</t>
+          <t>2253383</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-5.800%</t>
+          <t>10.700%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>2.700%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2751,7 +2899,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>LBPM-134347722</t>
+          <t>ALSE-134737223</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2761,12 +2909,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134737223/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2931,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01/01/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2793,65 +2946,70 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-104843</t>
+          <t>4607862</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1003</v>
+        <v>38731</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1492141</t>
+          <t>65826601</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-5.400%</t>
+          <t>350.000%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-7.600%</t>
+          <t>-59.000%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>LBPM-134347722</t>
+          <t>ALSE-134780087</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2024-12-12</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134780087/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2863,80 +3021,85 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01/21/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1118</t>
+          <t>396804</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3121</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>5668628</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.400%</t>
+          <t>312.400%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-7.000%</t>
+          <t>-12.800%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>LBPM-134347807</t>
+          <t>ALSE-134810468</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134810468/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2948,80 +3111,85 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01/21/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-56053</t>
+          <t>284293</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>301</v>
+        <v>2758</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1112402</t>
+          <t>4061334</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-12.400%</t>
+          <t>3.600%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>LBPM-134347807</t>
+          <t>ALSE-134813879</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134813879/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3033,80 +3201,85 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01/21/2025</t>
+          <t>03/02/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>The First Liberty Insurance Corporation</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>13.800%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-1386</t>
+          <t>223100</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>1959</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>3187140</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>117.200%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-9.400%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>LBPM-134347807</t>
+          <t>ALSE-134817781</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2024-12-13</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134817781/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3118,22 +3291,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>04/14/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3143,30 +3316,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>-12.100%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3176,7 +3326,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>ALSE-134865728</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3186,12 +3336,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134865728/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3358,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>01/28/2024</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3218,40 +3373,40 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1.300%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>394269</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2904</v>
+        <v>1963</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4824412</t>
+          <t>3285574</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>13.900%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-10.000%</t>
+          <t>6.200%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3261,7 +3416,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>LBPM-134399434</t>
+          <t>ALSE-133933153</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3271,12 +3426,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2023-12-22</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133933153/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3448,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>04/14/2024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3303,40 +3463,40 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.100%</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.100%</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>686363</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2385</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2206954</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>35.400%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.900%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3346,7 +3506,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>ALSE-134023631</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3356,12 +3516,17 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-03-07</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134023631/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -3373,22 +3538,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>08/19/2024</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3411,7 +3576,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3764291</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3431,7 +3596,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>LBPM-134488487</t>
+          <t>ALSE-134145696</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3441,12 +3606,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2024-06-21</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134145696/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3628,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>08/25/2024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3478,35 +3648,35 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>30.700%</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>30.700%</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>919714</t>
+          <t>1314773</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>82393</v>
+        <v>1778</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>65998147</t>
+          <t>4282647</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>88.700%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-3.500%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3516,7 +3686,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>ALSE-134198284</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3526,12 +3696,17 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-07-31</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134198284/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -3543,80 +3718,85 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>10/13/2024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Progressive Northern Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>16.900%</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>16.900%</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-1083</t>
+          <t>592164</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>211</v>
+        <v>2312</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>187367</t>
+          <t>3503931</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_disapproved</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>ALSE-134228318</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>DISAPPROVED</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2024-08-27</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134228318/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -3628,55 +3808,55 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/10/2025</t>
+          <t>03/16/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Progressive Northwestern Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>20.600%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.600%</t>
+          <t>20.600%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>460749</t>
+          <t>626568</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>82064</v>
+        <v>1825</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>79723926</t>
+          <t>3041592</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3686,7 +3866,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>PRGS-134368750</t>
+          <t>ALSE-134545996</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3696,12 +3876,17 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2025-01-10</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134545996/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3898,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>03/16/2025</t>
+          <t>09/01/2025</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3728,40 +3913,40 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>9.400%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>465032</t>
+          <t>405242</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>14290</v>
+        <v>785</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>5306519</t>
+          <t>3896556</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>19.900%</t>
+          <t>23.700%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.300%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3771,7 +3956,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>LBPM-134326132</t>
+          <t>ALSE-134592232</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3781,12 +3966,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134326132/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134592232/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3988,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3813,40 +4003,40 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-12.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-3246916</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>48818</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>106745</t>
+          <t>3030299</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3856,7 +4046,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>LBPM-134403897</t>
+          <t>GMMX-134491469</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3866,12 +4056,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134491469/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3883,55 +4078,55 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>01/01/2026</t>
+          <t>05/23/2024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>947532</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>19679</v>
+        <v>22932</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>48022559</t>
+          <t>34816544</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>5.800%</t>
+          <t>139.785%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.600%</t>
+          <t>-43.181%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3941,7 +4136,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>LBPM-134760659</t>
+          <t>GECC-133829918</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3951,12 +4146,17 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2023-10-06</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133829918/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -3968,12 +4168,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>08/02/2024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4002,21 +4202,21 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>20778</v>
+        <v>21983</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>27823328</t>
+          <t>34816544</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>41.700%</t>
+          <t>153.100%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>-44.300%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4026,7 +4226,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>GECC-133849972</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4036,12 +4236,17 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/133849972/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4258,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>08/03/2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4078,30 +4283,30 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.100%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1248566</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>290956</v>
+        <v>10440</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>238742051</t>
+          <t>40276329</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>24.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-26.900%</t>
+          <t>-49.300%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4111,7 +4316,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>SFMA-134294867</t>
+          <t>GECC-134085231</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4121,12 +4326,17 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134085231/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4138,12 +4348,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>09/26/2024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4153,12 +4363,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4168,25 +4378,25 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2937</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>22213</v>
+        <v>2018</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>28615291</t>
+          <t>4435498</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>47.900%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-13.500%</t>
+          <t>-13.700%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4196,7 +4406,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>SFMA-134329519</t>
+          <t>GECC-134128210</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4206,12 +4416,17 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134128210/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4223,12 +4438,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>09/26/2024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4238,40 +4453,40 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-5758545</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>356711</v>
+        <v>7001</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>261203324</t>
+          <t>12050233</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>42.700%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-17.100%</t>
+          <t>-30.500%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4281,7 +4496,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>SFMA-134329519</t>
+          <t>GECC-134128210</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4291,12 +4506,17 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134128210/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4308,12 +4528,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>09/26/2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4323,40 +4543,40 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-554469</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>20679</v>
+        <v>2455</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>26357498</t>
+          <t>4288629</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>388.400%</t>
+          <t>42.700%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-41.500%</t>
+          <t>-24.700%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4366,7 +4586,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>GECC-134128210</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4376,12 +4596,17 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134128210/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4393,12 +4618,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01/02/2026</t>
+          <t>09/26/2024</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4408,40 +4633,40 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-9.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-25716996</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>360274</v>
+        <v>28094</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>263832752</t>
+          <t>58817877</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>847.900%</t>
+          <t>46.400%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-52.200%</t>
+          <t>-27.400%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4451,7 +4676,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>SFMA-134676753</t>
+          <t>GECC-134128210</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4461,12 +4686,17 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134128210/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4478,55 +4708,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01/25/2025</t>
+          <t>09/26/2024</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>737882</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5911</v>
+        <v>10947</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>8890145</t>
+          <t>26950745</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>17.700%</t>
+          <t>49.000%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-18.300%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4536,7 +4766,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>TRVD-G134249162</t>
+          <t>GECC-134128210</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4546,12 +4776,17 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-04</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134128210/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -4563,50 +4798,50 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01/25/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>19.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>395965</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>17.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4616,27 +4851,32 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>TRVD-G134249162</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4648,12 +4888,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01/23/2026</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MGA Insurance Company, Inc.</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4668,60 +4908,65 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-51280</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>2534</v>
+        <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2226049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>rate_change</t>
+          <t>rate_change_withdrawn</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GNSC-134806133</t>
+          <t>GECC-134601148</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>FILED</t>
+          <t>WITHDRAWN</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134601148/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4733,12 +4978,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>07/08/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4751,32 +4996,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>138001</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4786,7 +5036,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>ALSE-134447963</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4796,12 +5046,17 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134447963/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4813,12 +5068,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>05/19/2025</t>
+          <t>05/08/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4851,7 +5106,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>103975400</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -4871,7 +5126,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ALSE-134490732</t>
+          <t>GECC-134653021</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4881,12 +5136,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134490732/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134653021/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -4898,12 +5158,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>04/03/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>GEICO Marine Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4913,40 +5173,40 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>-11.900%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.000%</t>
+          <t>-7.500%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>141982</t>
+          <t>-130787</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8410</v>
+        <v>1447</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2375260</t>
+          <t>1741509</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-11.500%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4956,7 +5216,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ALSE-134545039</t>
+          <t>GECC-134894381</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4966,12 +5226,5317 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/ID/134545039/filing_summary.pdf</t>
+          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>04/03/2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GEICO Casualty Company</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-12.400%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-7.500%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-617584</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>9434</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>8256468</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>-1.100%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>-11.700%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>GECC-134894381</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134894381/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>02/05/2024</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>30.800%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>22.900%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>440339</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>637</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1919511</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>37.000%</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>5.300%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>LBPM-133922253</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133922253/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>30.800%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>22.900%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>5126761</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>12875</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>22395182</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>32.400%</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>4.600%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>LBPM-133922784</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133922784/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>30.800%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>23.000%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>96071</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>2567</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>417123</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>25.400%</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>LBPM-133922784</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133922784/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>30.800%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>23.100%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>8080</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>21</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>35023</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>24.100%</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>20.900%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>LBPM-133923162</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133923162/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>30.800%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>23.000%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>189071</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>619</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>821042</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>24.600%</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>17.800%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>LBPM-133923162</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2023-12-18</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133923162/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>07/30/2024</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>LBPM-134157751</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134157751/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>07/30/2024</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>LBPM-134157751</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2024-06-27</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134157751/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>02/05/2025</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-7.000%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-137094</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>478</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>1960106</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>-6.300%</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>-11.000%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>LBPM-134347248</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134347248/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-7.000%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-4203</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>29</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>59666</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>-5.800%</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>-7.300%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LBPM-134347722</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>4.400%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-7.000%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-104843</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>1003</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>1492141</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>-5.400%</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>-7.600%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>LBPM-134347722</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134347722/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>01/21/2025</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-1118</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>4</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>21563</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0.400%</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-7.000%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>LBPM-134347807</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>01/21/2025</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-56053</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>301</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>1112402</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-12.400%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>LBPM-134347807</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>01/21/2025</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-1386</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>9</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>27910</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>-9.400%</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>LBPM-134347807</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134347807/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>12/19/2024</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-1.200%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>1121</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>-1.200%</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-1.200%</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>LBPM-134348285</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134348285/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>12/19/2024</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-5.000%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-254392</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>2920</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>5064518</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-10.500%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>LBPM-134348285</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134348285/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>07/21/2025</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>LBPM-134399434</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>07/21/2025</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>2904</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>4824412</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-10.000%</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>LBPM-134399434</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134399434/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>05/17/2025</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>LBPM-134488487</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>05/17/2025</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>LBPM-134488487</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134488487/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>01/23/2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MGA Insurance Company, Inc.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>3.700%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-51280</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2534</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2226049</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>GNSC-134806133</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>01/12/2024</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>6.700%</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>87320</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>2191</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>1559282</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>21.700%</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-1.800%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>PRGS-133878904</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133878904/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>01/12/2024</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>6.700%</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>5.500%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>130845</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>2857</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2379006</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>21.900%</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-1.800%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>PRGS-133878904</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2023-12-01</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133878904/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>12/06/2024</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-3.500%</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-1.300%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-60213</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>9011</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>4631734</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>90.500%</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>-45.700%</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>PRGS-134144916</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134144916/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>12/06/2024</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-3.500%</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-143631</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>9969</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>5745230</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>97.400%</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>-40.400%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>PRGS-134144916</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134144916/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>12/06/2024</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-1.700%</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-94715</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>13488</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>4305212</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>178.500%</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>-64.300%</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>PRGS-134147799</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134147799/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>12/06/2024</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-1.700%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-124562</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>13760</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>4982482</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>180.270%</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-63.570%</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>PRGS-134147799</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134147799/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>09/27/2024</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.063%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1.437%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>866501</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>75366</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>60303970</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>9.300%</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>-27.500%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>PRGS-134218749</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134218749/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>09/27/2024</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0.207%</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.097%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>217</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>191106</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>-14.100%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>PRGS-134218749</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134218749/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>09/27/2024</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0.207%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0.097%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>68520</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>74343</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>70818463</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>9.300%</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-36.600%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>PRGS-134218749</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134218749/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2.900%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1.400%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>919714</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>82393</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>65998147</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>13.500%</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-3.500%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>PRGS-134368750</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1.100%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-0.600%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-1083</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>211</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>187367</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>3.300%</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>PRGS-134368750</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1.100%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-0.600%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>460749</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>82064</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>79723926</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>10.600%</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-4.400%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>PRGS-134368750</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134368750/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>03/16/2024</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>11.300%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>11.300%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>659888</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>15631</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>5835707</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>274.000%</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-82.000%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>LBPM-133801944</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2023-09-01</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133801944/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>02/19/2024</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>44.600%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>19.300%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>9761919</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>36218</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>50556461</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>46.200%</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>LBPM-133968105</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2024-01-30</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133968105/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>12/13/2024</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-14.400%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-4.000%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-5219358</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>57970</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>130041966</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-7.600%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>LBPM-134272035</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134272035/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>11/11/2024</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>29.000%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>15.800%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>8602272</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>32220</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>54340225</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>23.200%</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>LBPM-134277608</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134277608/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>03/16/2025</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>9.400%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>465032</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>14290</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>5306519</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>19.900%</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>LBPM-134326132</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2024-11-22</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134326132/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-12.700%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-3246916</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>48818</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>106745</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-7.300%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>LBPM-134403897</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2025-02-07</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134403897/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>01/01/2026</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>4.500%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2.000%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>947532</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>19679</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>48022559</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>5.800%</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0.600%</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>LBPM-134760659</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134760659/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0.100%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>15351</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>19131</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>18529005</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>23.100%</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-19.100%</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>SFMA-133807390</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133807390/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>01/01/2024</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-0.400%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-370799</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>273008</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>161575645</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>30.800%</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-26.100%</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>SFMA-133807390</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2023-11-03</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133807390/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>01/15/2024</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>16.100%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>11.600%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>10307513</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>113136</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>89170406</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>49.700%</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-23.900%</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>SFMA-133920834</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2023-12-13</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133920834/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>03/04/2024</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>23.700%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2412338</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>20803</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>24350697</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>34.000%</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-0.100%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>SFMA-133934434</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133934434/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>03/04/2024</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>12.700%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>10.700%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>23282535</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>338036</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>216795779</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>54.500%</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-0.500%</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>SFMA-133934434</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133934434/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>04/01/2024</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>-3532</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>3500</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2216021</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-11.400%</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>SFMA-133987158</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2024-02-19</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133987158/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>08/01/2024</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>895</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>348319</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>SFMA-134083852</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134083852/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>08/01/2024</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>11338</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2415130</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>9.500%</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-9.000%</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>SFMA-134083852</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134083852/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10/15/2024</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>15.100%</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>11.400%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>12161053</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>119007</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>106561382</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>18.800%</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>SFMA-134197056</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2024-08-29</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134197056/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>20778</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>27823328</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>41.700%</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-26.900%</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>SFMA-134294867</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>04/15/2025</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>290956</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>238742051</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>24.500%</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-26.900%</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>SFMA-134294867</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134294867/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>02/03/2025</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>22213</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>28615291</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>19.400%</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-13.500%</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>SFMA-134329519</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>02/03/2025</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-0.200%</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-2.200%</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-5758545</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>356711</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>261203324</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-17.100%</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>SFMA-134329519</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134329519/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>15.900%</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-2.100%</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-554469</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>20679</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>26357498</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>388.400%</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-41.500%</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>SFMA-134676753</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>01/02/2026</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-2.600%</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-9.700%</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-25716996</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>360274</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>263832752</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>847.900%</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>-52.200%</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>SFMA-134676753</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134676753/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>01/27/2024</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>16.100%</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>13.400%</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>1104984</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>6659</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>8246148</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>24.100%</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>TRVD-133877224</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133877224/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>01/27/2024</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>16.100%</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>14.000%</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>53022</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>319</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>378729</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>22.100%</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>TRVD-133877224</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2023-11-16</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/133877224/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>01/25/2025</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>19.100%</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>8.300%</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>737882</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>5911</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>8890145</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>17.700%</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>TRVD-G134249162</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>01/25/2025</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>19.100%</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>34845</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>280</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>395965</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>17.200%</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>TRVD-G134249162</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134254872/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R113"/>
+  <dimension ref="A1:T113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,6 +707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -957,6 +1007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1047,6 +1107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1137,6 +1207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1227,6 +1307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1317,6 +1407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1407,6 +1507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1497,6 +1607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1587,6 +1707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1672,6 +1802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1759,7 +1899,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1999,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1939,7 +2099,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2199,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2299,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2394,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2494,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2594,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2689,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2789,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2889,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2989,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2829,7 +3089,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2919,7 +3189,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3289,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3389,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3189,7 +3489,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3589,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3666,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3439,6 +3769,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3529,6 +3869,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3619,6 +3969,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3709,6 +4069,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3799,6 +4169,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3886,7 +4266,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3976,7 +4366,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4466,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4159,6 +4569,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4249,6 +4669,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4339,6 +4769,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4429,6 +4869,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4519,6 +4969,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4609,6 +5069,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4699,6 +5169,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4789,6 +5269,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4876,7 +5366,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5466,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5566,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5666,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5766,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5866,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5419,6 +5969,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5509,6 +6069,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5599,6 +6169,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5689,6 +6269,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5779,6 +6369,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5869,6 +6469,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5959,6 +6569,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6046,7 +6666,17 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6766,17 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6866,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6966,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6406,7 +7066,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6496,7 +7166,17 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6589,6 +7269,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6679,6 +7369,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6766,7 +7466,17 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6856,7 +7566,17 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6946,7 +7666,17 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7766,17 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7126,7 +7866,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7219,6 +7969,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7309,6 +8069,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -7394,6 +8164,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7479,6 +8259,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7569,6 +8359,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7659,6 +8459,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7749,6 +8559,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7839,6 +8659,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7929,6 +8759,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8016,7 +8856,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8106,7 +8956,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8196,7 +9056,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8289,6 +9159,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -8379,6 +9259,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8469,6 +9359,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8559,6 +9459,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8646,7 +9556,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8736,7 +9656,17 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8826,7 +9756,17 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8919,6 +9859,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9009,6 +9959,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9099,6 +10059,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9189,6 +10159,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9279,6 +10259,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9369,6 +10359,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9459,6 +10459,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9549,6 +10559,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9639,6 +10659,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9726,7 +10756,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9816,7 +10856,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9906,7 +10956,17 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9996,7 +11056,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10089,6 +11159,16 @@
           <t>ambest_validated</t>
         </is>
       </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -10179,6 +11259,16 @@
           <t>ambest_validated</t>
         </is>
       </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -10269,6 +11359,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -10359,6 +11459,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -10446,7 +11556,17 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10536,7 +11656,17 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T113"/>
+  <dimension ref="A1:U113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,9 +619,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,9 +720,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,9 +821,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,9 +922,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,9 +1023,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1114,9 +1124,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1214,9 +1225,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1314,9 +1326,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,9 +1427,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1514,9 +1528,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1614,9 +1629,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1714,9 +1730,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1809,9 +1826,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1909,9 +1927,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2009,9 +2028,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2109,9 +2129,10 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2209,9 +2230,10 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2309,9 +2331,10 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2404,9 +2427,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2504,9 +2528,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2604,9 +2629,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2699,9 +2725,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2799,9 +2826,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2899,9 +2927,10 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2999,9 +3028,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3099,9 +3129,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3199,9 +3230,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3299,9 +3331,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3399,9 +3432,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3499,9 +3533,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3599,9 +3634,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3676,9 +3712,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3776,9 +3813,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3876,9 +3914,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3976,9 +4015,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4076,9 +4116,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4176,9 +4217,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4276,9 +4318,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4376,9 +4419,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4476,9 +4520,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4576,9 +4621,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4676,9 +4722,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4776,9 +4823,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4876,9 +4924,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4976,9 +5025,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5076,9 +5126,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5176,9 +5227,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5276,9 +5328,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5376,9 +5429,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5476,9 +5530,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5576,9 +5631,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5676,9 +5732,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5776,9 +5833,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5876,9 +5934,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5976,9 +6035,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6076,9 +6136,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6176,9 +6237,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6276,9 +6338,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6376,9 +6439,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6476,9 +6540,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6576,9 +6641,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6676,9 +6742,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6776,9 +6843,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6876,9 +6944,10 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6976,9 +7045,10 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7076,9 +7146,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7176,9 +7247,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7276,9 +7348,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7376,9 +7449,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7476,9 +7550,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7576,9 +7651,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7676,9 +7752,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7776,9 +7853,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7876,9 +7954,10 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7976,9 +8055,10 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8076,9 +8156,10 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8171,9 +8252,10 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8266,9 +8348,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8366,9 +8449,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8466,9 +8550,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8566,9 +8651,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8666,9 +8752,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8766,9 +8853,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8866,9 +8954,10 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8966,9 +9055,10 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9066,9 +9156,10 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9166,9 +9257,10 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9266,9 +9358,10 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9366,9 +9459,10 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9466,9 +9560,10 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9566,9 +9661,10 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9666,9 +9762,10 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9766,9 +9863,10 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9866,9 +9964,10 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9966,9 +10065,10 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10066,9 +10166,10 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10166,9 +10267,10 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10266,9 +10368,10 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10366,9 +10469,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10466,9 +10570,10 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10566,9 +10671,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10666,9 +10772,10 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10766,9 +10873,10 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10866,9 +10974,10 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10966,9 +11075,10 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11066,9 +11176,10 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11166,7 +11277,12 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>field_validated</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>field</t>
         </is>
       </c>
     </row>
@@ -11266,7 +11382,12 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>field_validated</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>field</t>
         </is>
       </c>
     </row>
@@ -11366,9 +11487,10 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11466,9 +11588,10 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11566,9 +11689,10 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11666,9 +11790,10 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/id_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/id_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U123"/>
+  <dimension ref="A1:U149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12707,98 +12707,2544 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>15761</v>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>21117430</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>22.400%</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-29.500%</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>SFMA-134834321</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134834321/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>10/02/2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>312789</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>261114137</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>29.700%</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>-62.600%</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>SFMA-134834321</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134834321/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-7.600%</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-5.700%</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>3962738</t>
+        </is>
+      </c>
+      <c r="I125" t="n">
+        <v>96641</v>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>70000302</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>182.700%</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-44.600%</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>PRGS-134880508</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>PENDING ACTUARY REVIEW</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134880508/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Progressive Northern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-8.800%</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-6.700%</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>13522</t>
+        </is>
+      </c>
+      <c r="I126" t="n">
+        <v>195</v>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>200640</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>49.400%</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>-21.000%</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>PRGS-134880508</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>PENDING ACTUARY REVIEW</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134880508/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>04/10/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Progressive Northwestern Insurance Company</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-8.800%</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-6.700%</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>6105120</t>
+        </is>
+      </c>
+      <c r="I127" t="n">
+        <v>90431</v>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>90585504</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>195.300%</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>-48.000%</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>PRGS-134880508</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>PENDING ACTUARY REVIEW</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134880508/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>05/25/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>94563773</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ALSE-134914584</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134914584/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="I129" t="n">
+        <v>411</v>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>693357</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>ALSE-134944709</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134944709/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Allstate North American Insurance Company</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>12.600%</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I130" t="n">
+        <v>10432</v>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>15835415</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>15.000%</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ALSE-135026561</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135026561/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>46692</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>370</v>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>1542192</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2.600%</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>LBPM-134943365</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134943365/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="I132" t="n">
+        <v>52</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>108347</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>3.400%</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>LBPM-134942977</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134942977/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>153444</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>3397</v>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>5134354</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>3.600%</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2.200%</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>LBPM-134942977</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134942977/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>06/21/2026</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>5.400%</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>5.400%</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>252653</t>
+        </is>
+      </c>
+      <c r="I134" t="n">
+        <v>12837</v>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>4665548</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>LBPM-134953058</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134953058/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>05/27/2026</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>5.600%</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>489389</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>6856</v>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>16350659</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>7.100%</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>1.100%</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>LBPM-134943247</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134943247/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>08/23/2026</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TravCo Insurance Company</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>23571</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>32838026</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>96.900%</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-17.700%</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>TRVD-G134968715</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>DISAPPROVED</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134978514/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>08/23/2026</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TravCo Insurance Company</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>23571</v>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>32838026</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>96.900%</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-17.700%</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>TRVD-G134989844</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135000663/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>09/03/2026</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Nationwide Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-10.000%</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-194014</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>971</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>1944142</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>-19.300%</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>NWPP-G135036796</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135042178/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>-12.200%</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-1872905</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>12898</v>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>31059365</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-12.700%</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>AMFC-135027471</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135027471/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>08/11/2026</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>-12.200%</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-6.000%</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-1872905</t>
+        </is>
+      </c>
+      <c r="I140" t="n">
+        <v>12898</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>31059365</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>1.300%</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-12.700%</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>rate_change_disapproved</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>AMFC-135023971</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>DISAPPROVED</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135023971/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>12/03/2026</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>American Family Insurance Company</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I141" t="n">
+        <v>12718</v>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>31112965</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>271.270%</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-62.310%</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>AMFC-135038153</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135038153/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>COUNTRY Preferred Insurance Company</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-0.537%</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-0.026%</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-2003</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>5099</v>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>7817446</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>30.600%</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>-12.800%</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>CFPC-134926625</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134926625/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>07/17/2026</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Farmers Direct Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>3457</v>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>5259168</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>FAIG-135014287</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>FILED</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/135014287/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>05/03/2026</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Farmers Insurance Company of Idaho</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2.700%</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>1870412</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>34881</v>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>69636645</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>14.100%</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>-4.200%</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>FARM-134934609</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134934609/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>02/26/2027</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>4684</v>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>10043882</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>292.600%</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>-57.700%</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>USAA-134993880</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134994186/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>02/26/2027</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>12312</v>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>30796673</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>313.000%</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>-61.200%</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>USAA-134993880</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134994186/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>02/26/2027</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>10616</v>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>23152620</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>327.900%</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>-65.400%</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>USAA-134993880</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134994186/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>02/26/2027</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>7417</v>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>16099371</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>335.000%</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>-51.600%</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>rate_change_pending</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>USAA-134993880</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>output/pdfs/ID/134994186/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
           <t>01/23/2026</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C149" t="inlineStr">
         <is>
           <t>MGA Insurance Company, Inc.</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D149" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
+      <c r="E149" t="inlineStr">
         <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F149" t="inlineStr">
         <is>
           <t>3.700%</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="G149" t="inlineStr">
         <is>
           <t>-0.100%</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>-51280</t>
         </is>
       </c>
-      <c r="I123" t="n">
+      <c r="I149" t="n">
         <v>2534</v>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t>2226049</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K149" t="inlineStr">
         <is>
           <t>15.000%</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
+      <c r="L149" t="inlineStr">
         <is>
           <t>15.000%</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr">
+      <c r="M149" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr">
+      <c r="N149" t="inlineStr">
         <is>
           <t>GNSC-134806133</t>
         </is>
       </c>
-      <c r="O123" t="inlineStr">
+      <c r="O149" t="inlineStr">
         <is>
           <t>FILED</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr">
+      <c r="P149" t="inlineStr">
         <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="Q123" t="inlineStr">
+      <c r="Q149" t="inlineStr">
         <is>
           <t>output/pdfs/ID/134806133/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R123" t="inlineStr">
+      <c r="R149" t="inlineStr">
         <is>
           <t>pipeline_only</t>
         </is>
       </c>
-      <c r="S123" t="inlineStr">
+      <c r="S149" t="inlineStr">
         <is>
           <t>original</t>
         </is>
       </c>
-      <c r="T123" t="inlineStr">
+      <c r="T149" t="inlineStr">
         <is>
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
